--- a/docs/sdlc/20_design/WS2D-IF-001_APIエンドポイント一覧.xlsx
+++ b/docs/sdlc/20_design/WS2D-IF-001_APIエンドポイント一覧.xlsx
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="103">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="105">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="108">
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109">

--- a/docs/sdlc/20_design/WS2D-IF-001_APIエンドポイント一覧.xlsx
+++ b/docs/sdlc/20_design/WS2D-IF-001_APIエンドポイント一覧.xlsx
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="52">
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54">
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56">
